--- a/Data/National Accounts/PSA-17FIA_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-17FIA_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F49611-77AC-4907-AAB6-1C99F9CF956C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADF3596-FDD9-4673-A25A-FDBDD2C15CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIA" sheetId="1" r:id="rId1"/>
@@ -619,9 +619,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -629,6 +626,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -23586,7 +23586,7 @@
     </row>
     <row r="3" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:96" x14ac:dyDescent="0.2">
@@ -23596,7 +23596,7 @@
     </row>
     <row r="6" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:96" x14ac:dyDescent="0.2">
@@ -23798,10 +23798,10 @@
         <v>1372132.1156776433</v>
       </c>
       <c r="Z12" s="8">
-        <v>1556516.0156128821</v>
+        <v>1555122.950657133</v>
       </c>
       <c r="AA12" s="8">
-        <v>1649159.0713213254</v>
+        <v>1650306.334036835</v>
       </c>
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
@@ -23950,10 +23950,10 @@
         <v>759945.80269620812</v>
       </c>
       <c r="Z13" s="8">
-        <v>842456.8631757145</v>
+        <v>842908.5450948677</v>
       </c>
       <c r="AA13" s="8">
-        <v>900778.4624606237</v>
+        <v>898481.57161434984</v>
       </c>
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
@@ -24102,10 +24102,10 @@
         <v>304569.36096480803</v>
       </c>
       <c r="Z14" s="8">
-        <v>337492.08158491872</v>
+        <v>337736.38086831069</v>
       </c>
       <c r="AA14" s="8">
-        <v>380558.91447084676</v>
+        <v>381595.35950284154</v>
       </c>
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
@@ -24254,10 +24254,10 @@
         <v>128418.98592527377</v>
       </c>
       <c r="Z15" s="8">
-        <v>150815.53109932554</v>
+        <v>151695.23374785658</v>
       </c>
       <c r="AA15" s="8">
-        <v>174973.15110229631</v>
+        <v>176038.04418150452</v>
       </c>
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
@@ -24504,10 +24504,10 @@
         <v>2565066.2652639337</v>
       </c>
       <c r="Z17" s="11">
-        <v>2887280.4914728408</v>
+        <v>2887463.110368168</v>
       </c>
       <c r="AA17" s="11">
-        <v>3105469.5993550923</v>
+        <v>3106421.3093355307</v>
       </c>
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
@@ -24821,7 +24821,7 @@
     </row>
     <row r="24" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:96" x14ac:dyDescent="0.2">
@@ -24831,7 +24831,7 @@
     </row>
     <row r="27" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:96" x14ac:dyDescent="0.2">
@@ -25033,10 +25033,10 @@
         <v>1150598.9723867162</v>
       </c>
       <c r="Z33" s="8">
-        <v>1263085.3491931434</v>
+        <v>1261957.4475215692</v>
       </c>
       <c r="AA33" s="8">
-        <v>1316161.0799220488</v>
+        <v>1317224.6665972352</v>
       </c>
       <c r="AB33" s="9"/>
       <c r="AC33" s="9"/>
@@ -25185,10 +25185,10 @@
         <v>643415.55614843487</v>
       </c>
       <c r="Z34" s="8">
-        <v>690781.96492417785</v>
+        <v>691139.06059200526</v>
       </c>
       <c r="AA34" s="8">
-        <v>727006.44313719193</v>
+        <v>725258.54074424517</v>
       </c>
       <c r="AB34" s="9"/>
       <c r="AC34" s="9"/>
@@ -25337,10 +25337,10 @@
         <v>259722.67821384859</v>
       </c>
       <c r="Z35" s="8">
-        <v>278469.03713858617</v>
+        <v>278675.12322198751</v>
       </c>
       <c r="AA35" s="8">
-        <v>308943.38181452308</v>
+        <v>309857.73560986272</v>
       </c>
       <c r="AB35" s="9"/>
       <c r="AC35" s="9"/>
@@ -25489,10 +25489,10 @@
         <v>107090.21096232953</v>
       </c>
       <c r="Z36" s="8">
-        <v>121252.00493167926</v>
+        <v>121961.32875487773</v>
       </c>
       <c r="AA36" s="8">
-        <v>138565.9529203822</v>
+        <v>139476.95933861661</v>
       </c>
       <c r="AB36" s="9"/>
       <c r="AC36" s="9"/>
@@ -25739,10 +25739,10 @@
         <v>2160827.4177113287</v>
       </c>
       <c r="Z38" s="11">
-        <v>2353588.3561875871</v>
+        <v>2353732.9600904398</v>
       </c>
       <c r="AA38" s="11">
-        <v>2490676.8577941461</v>
+        <v>2491817.9022899596</v>
       </c>
       <c r="AB38" s="9"/>
       <c r="AC38" s="9"/>
@@ -26056,7 +26056,7 @@
     </row>
     <row r="45" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:96" x14ac:dyDescent="0.2">
@@ -26066,7 +26066,7 @@
     </row>
     <row r="48" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:91" x14ac:dyDescent="0.2">
@@ -26182,7 +26182,7 @@
         <v>48</v>
       </c>
       <c r="Z52" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA52" s="16"/>
     </row>
@@ -26263,10 +26263,10 @@
         <v>18.630547537667582</v>
       </c>
       <c r="Y54" s="17">
-        <v>13.43776578279261</v>
+        <v>13.336240212489841</v>
       </c>
       <c r="Z54" s="17">
-        <v>5.9519500460754955</v>
+        <v>6.1206339562721581</v>
       </c>
       <c r="AA54" s="17"/>
       <c r="AB54" s="9"/>
@@ -26408,10 +26408,10 @@
         <v>13.225543408342077</v>
       </c>
       <c r="Y55" s="17">
-        <v>10.857492756294704</v>
+        <v>10.91692882628162</v>
       </c>
       <c r="Z55" s="17">
-        <v>6.9227994730864708</v>
+        <v>6.5930078468035447</v>
       </c>
       <c r="AA55" s="17"/>
       <c r="AB55" s="9"/>
@@ -26553,10 +26553,10 @@
         <v>7.0980541746406658</v>
       </c>
       <c r="Y56" s="17">
-        <v>10.809597037541408</v>
+        <v>10.889808416196871</v>
       </c>
       <c r="Z56" s="17">
-        <v>12.760842471823054</v>
+        <v>12.986157582955869</v>
       </c>
       <c r="AA56" s="17"/>
       <c r="AB56" s="9"/>
@@ -26698,10 +26698,10 @@
         <v>14.181467532941539</v>
       </c>
       <c r="Y57" s="17">
-        <v>17.440213386425739</v>
+        <v>18.125238768142211</v>
       </c>
       <c r="Z57" s="17">
-        <v>16.017992196745851</v>
+        <v>16.047182124462694</v>
       </c>
       <c r="AA57" s="17"/>
       <c r="AB57" s="9"/>
@@ -26936,10 +26936,10 @@
         <v>15.300730010466367</v>
       </c>
       <c r="Y59" s="17">
-        <v>12.561633614395234</v>
+        <v>12.568753075510159</v>
       </c>
       <c r="Z59" s="17">
-        <v>7.5569072186315367</v>
+        <v>7.5830648080364256</v>
       </c>
       <c r="AA59" s="17"/>
       <c r="AB59" s="9"/>
@@ -27239,7 +27239,7 @@
     </row>
     <row r="66" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:91" x14ac:dyDescent="0.2">
@@ -27249,7 +27249,7 @@
     </row>
     <row r="69" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="1:91" x14ac:dyDescent="0.2">
@@ -27365,7 +27365,7 @@
         <v>48</v>
       </c>
       <c r="Z73" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA73" s="16"/>
     </row>
@@ -27446,10 +27446,10 @@
         <v>11.596408011865918</v>
       </c>
       <c r="Y75" s="17">
-        <v>9.7763321110129198</v>
+        <v>9.6783047618979907</v>
       </c>
       <c r="Z75" s="17">
-        <v>4.2020700155227075</v>
+        <v>4.3794835700846022</v>
       </c>
       <c r="AA75" s="17"/>
       <c r="AB75" s="9"/>
@@ -27591,10 +27591,10 @@
         <v>7.2496462842228624</v>
       </c>
       <c r="Y76" s="17">
-        <v>7.3617133317826813</v>
+        <v>7.417213337092619</v>
       </c>
       <c r="Z76" s="17">
-        <v>5.2439814662778872</v>
+        <v>4.9367026258093887</v>
       </c>
       <c r="AA76" s="17"/>
       <c r="AB76" s="9"/>
@@ -27736,10 +27736,10 @@
         <v>1.1841683763373396</v>
       </c>
       <c r="Y77" s="17">
-        <v>7.2178367532858942</v>
+        <v>7.2971852664071264</v>
       </c>
       <c r="Z77" s="17">
-        <v>10.943530738309931</v>
+        <v>11.189593110195091</v>
       </c>
       <c r="AA77" s="17"/>
       <c r="AB77" s="9"/>
@@ -27881,10 +27881,10 @@
         <v>7.7742375524022123</v>
       </c>
       <c r="Y78" s="17">
-        <v>13.224172258220079</v>
+        <v>13.886533287136132</v>
       </c>
       <c r="Z78" s="17">
-        <v>14.279308617171878</v>
+        <v>14.361626560286524</v>
       </c>
       <c r="AA78" s="17"/>
       <c r="AB78" s="9"/>
@@ -28119,10 +28119,10 @@
         <v>8.7478225745282856</v>
       </c>
       <c r="Y80" s="17">
-        <v>8.9207003250830468</v>
+        <v>8.9273923867288545</v>
       </c>
       <c r="Z80" s="17">
-        <v>5.8246592377190041</v>
+        <v>5.8666358733496367</v>
       </c>
       <c r="AA80" s="17"/>
       <c r="AB80" s="9"/>
@@ -28418,7 +28418,7 @@
     </row>
     <row r="86" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88" spans="1:96" x14ac:dyDescent="0.2">
@@ -28428,7 +28428,7 @@
     </row>
     <row r="89" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90" spans="1:96" x14ac:dyDescent="0.2">
@@ -28630,10 +28630,10 @@
         <v>119.25372337430437</v>
       </c>
       <c r="Z95" s="17">
-        <v>123.23126197348276</v>
+        <v>123.23101335241758</v>
       </c>
       <c r="AA95" s="17">
-        <v>125.30070190337179</v>
+        <v>125.28662542435104</v>
       </c>
       <c r="AB95" s="9"/>
       <c r="AC95" s="9"/>
@@ -28782,10 +28782,10 @@
         <v>118.11119507979224</v>
       </c>
       <c r="Z96" s="17">
-        <v>121.95698584403327</v>
+        <v>121.95932673416867</v>
       </c>
       <c r="AA96" s="17">
-        <v>123.90240429968784</v>
+        <v>123.88431450836094</v>
       </c>
       <c r="AB96" s="9"/>
       <c r="AC96" s="9"/>
@@ -28934,10 +28934,10 @@
         <v>117.26714165254137</v>
       </c>
       <c r="Z97" s="17">
-        <v>121.19555015984002</v>
+        <v>121.19358806177904</v>
       </c>
       <c r="AA97" s="17">
-        <v>123.18079521098745</v>
+        <v>123.15179375844359</v>
       </c>
       <c r="AB97" s="9"/>
       <c r="AC97" s="9"/>
@@ -29086,10 +29086,10 @@
         <v>119.91664296043542</v>
       </c>
       <c r="Z98" s="17">
-        <v>124.38188645565423</v>
+        <v>124.37978111302732</v>
       </c>
       <c r="AA98" s="17">
-        <v>126.27427402951798</v>
+        <v>126.21299246574939</v>
       </c>
       <c r="AB98" s="9"/>
       <c r="AC98" s="9"/>
@@ -29336,10 +29336,10 @@
         <v>118.70759525907721</v>
       </c>
       <c r="Z100" s="17">
-        <v>122.67567877289061</v>
+        <v>122.67590076391758</v>
       </c>
       <c r="AA100" s="17">
-        <v>124.68376175082921</v>
+        <v>124.66486040094486</v>
       </c>
       <c r="AB100" s="9"/>
       <c r="AC100" s="9"/>
@@ -29457,7 +29457,7 @@
     </row>
     <row r="107" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="109" spans="1:96" x14ac:dyDescent="0.2">
@@ -29467,7 +29467,7 @@
     </row>
     <row r="110" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="111" spans="1:96" x14ac:dyDescent="0.2">
@@ -29669,10 +29669,10 @@
         <v>53.493047499747817</v>
       </c>
       <c r="Z116" s="17">
-        <v>53.909414766241923</v>
+        <v>53.857759951047335</v>
       </c>
       <c r="AA116" s="17">
-        <v>53.10498198609973</v>
+        <v>53.125644260721302</v>
       </c>
       <c r="AB116" s="9"/>
       <c r="AC116" s="9"/>
@@ -29821,10 +29821,10 @@
         <v>29.626751284650073</v>
       </c>
       <c r="Z117" s="17">
-        <v>29.178213397132257</v>
+        <v>29.192010871695327</v>
       </c>
       <c r="AA117" s="17">
-        <v>29.006191612620739</v>
+        <v>28.923364931672346</v>
       </c>
       <c r="AB117" s="9"/>
       <c r="AC117" s="9"/>
@@ -29973,10 +29973,10 @@
         <v>11.873742409281158</v>
       </c>
       <c r="Z118" s="17">
-        <v>11.688926052790924</v>
+        <v>11.696647470770539</v>
       </c>
       <c r="AA118" s="17">
-        <v>12.254472384784473</v>
+        <v>12.284082598714386</v>
       </c>
       <c r="AB118" s="9"/>
       <c r="AC118" s="9"/>
@@ -30125,10 +30125,10 @@
         <v>5.0064588063209365</v>
       </c>
       <c r="Z119" s="17">
-        <v>5.2234457838348947</v>
+        <v>5.2535817064867905</v>
       </c>
       <c r="AA119" s="17">
-        <v>5.6343540164950472</v>
+        <v>5.6669082088919671</v>
       </c>
       <c r="AB119" s="9"/>
       <c r="AC119" s="9"/>
@@ -30692,7 +30692,7 @@
     </row>
     <row r="128" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="130" spans="1:96" x14ac:dyDescent="0.2">
@@ -30702,7 +30702,7 @@
     </row>
     <row r="131" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="132" spans="1:96" x14ac:dyDescent="0.2">
@@ -30904,10 +30904,10 @@
         <v>53.248073536820883</v>
       </c>
       <c r="Z137" s="17">
-        <v>53.666366332604007</v>
+        <v>53.615149590847381</v>
       </c>
       <c r="AA137" s="17">
-        <v>52.843510221060932</v>
+        <v>52.861995468718511</v>
       </c>
       <c r="AB137" s="9"/>
       <c r="AC137" s="9"/>
@@ -31056,10 +31056,10 @@
         <v>29.776350988267154</v>
       </c>
       <c r="Z138" s="17">
-        <v>29.350160707079944</v>
+        <v>29.36352901161094</v>
       </c>
       <c r="AA138" s="17">
-        <v>29.189111420140673</v>
+        <v>29.105599573618068</v>
       </c>
       <c r="AB138" s="9"/>
       <c r="AC138" s="9"/>
@@ -31208,10 +31208,10 @@
         <v>12.01959379472043</v>
       </c>
       <c r="Z139" s="17">
-        <v>11.831679758547864</v>
+        <v>11.839708579824608</v>
       </c>
       <c r="AA139" s="17">
-        <v>12.403992948653205</v>
+        <v>12.435007201975155</v>
       </c>
       <c r="AB139" s="9"/>
       <c r="AC139" s="9"/>
@@ -31360,10 +31360,10 @@
         <v>4.9559816801915471</v>
       </c>
       <c r="Z140" s="17">
-        <v>5.1517932017681662</v>
+        <v>5.1816128177170739</v>
       </c>
       <c r="AA140" s="17">
-        <v>5.5633854101451909</v>
+        <v>5.5973977556882648</v>
       </c>
       <c r="AB140" s="9"/>
       <c r="AC140" s="9"/>
